--- a/02_加值成品/八上/八上5-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上5-3 熱的傳播　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上5-3 熱的傳播　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>熱靠粒子碰撞傳遞是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>傳導</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>傳導對流輻射</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>輻射</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>良導體</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>固體為主</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>熱靠流體流動傳遞是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>只能靠輻射</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>對流</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>液氣</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>熱以電磁波傳遞是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>輻射</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>空氣不良導體</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>只能靠輻射</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>不需介質</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>金屬是熱的？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>傳導</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>傳導對流輻射</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>良導體</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>傳導快</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>哪種傳播不需要介質？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>傳導對流輻射</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>不良導體</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>良導體</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>輻射</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>真空可</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>對流中熱流體會？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>上升</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>傳導</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>良導體</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>對流</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>冷下降</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>太陽的熱靠什麼到地球？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>熱空氣上升</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>對流</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>輻射</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>良導體</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>真空傳播</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>空氣是熱的？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>傳導</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>不良導體</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>傳導對流輻射</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>保溫</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>熱的三種傳播方式是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>輻射</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>傳導對流輻射</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>傳導</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>對流</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>三種</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>鍋子把手用木頭因為木是熱的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>只能靠輻射</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>傳導對流輻射</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>不良導體</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>熱空氣上升</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>絕熱</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上5-3 熱的傳播　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上5-3 熱的傳播　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>鐵湯匙放熱湯柄變燙是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>良導體</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>傳導</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>對流</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>沿金屬</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>燒開水底部加熱靠？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>傳導</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>對流</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>良導體</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>輻射</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>水循環</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>冷氣裝高處因為？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>冷空氣下沉對流</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>熱氣上升形成對流抽氣</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>受熱膨脹密度變小上升</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>反射輻射吸熱少</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>循環佳</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>暖氣裝低處因為？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>傳導對流輻射</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>熱空氣上升</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>對流</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>保溫瓶鍍銀為了減少？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>輻射</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>固體能對流嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>輻射</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>傳導對流輻射</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>粒子不流動</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>深色衣物較易？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>吸熱</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>良導體</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>對流</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>輻射吸收</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>羽絨衣保暖靠？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>只能靠輻射</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>輻射</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>空氣不良導體</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>阻傳導</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>用火烤手取暖主要靠？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>輻射</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>傳導</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>只能靠輻射</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>輻射</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>液體與氣體受熱主要靠哪種傳播？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>傳導</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>對流</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>對流</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上5-3 熱的傳播　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上5-3 熱的傳播　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>保溫瓶如何同時阻三種傳熱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>真空阻傳導對流、鍍銀阻輻射</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>熱氣上升形成對流抽氣</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>增大表面積加速散熱</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>夜間地表輻射散熱快</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>綜合設計</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何海陸風是對流現象？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>陸海升溫不同造成空氣對流</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>傳導(熱由手傳向冰)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>熱氣上升形成對流抽氣</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>冷空氣下沉對流</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>煙囪為何能助燃？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>熱氣上升形成對流抽氣</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>冷空氣下沉對流</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>反射輻射吸熱少</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>受熱膨脹密度變小上升</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>對流</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>散熱片為何做很多鰭片？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>增大表面積加速散熱</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>真空阻傳導對流、鍍銀阻輻射</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>夜間地表輻射散熱快</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>冷空氣下沉對流</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>面積</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>沙漠日夜溫差大與輻射關係？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>熱氣上升形成對流抽氣</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>冷空氣下沉對流</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>夜間地表輻射散熱快</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>陸海升溫不同造成空氣對流</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>輻射</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>真空中兩物體如何傳熱？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>只能靠輻射</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>不良導體</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>空氣不良導體</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>傳導對流輻射</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>無介質</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>手握冰塊覺得冷是何傳播？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>真空阻傳導對流、鍍銀阻輻射</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>傳導(熱由手傳向冰)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>夜間地表輻射散熱快</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>熱氣上升形成對流抽氣</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>淺色屋頂較涼因為？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>傳導(熱由手傳向冰)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>反射輻射吸熱少</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>真空阻傳導對流、鍍銀阻輻射</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>夜間地表輻射散熱快</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何暖空氣會上升形成對流？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>受熱膨脹密度變小上升</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>增大表面積加速散熱</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>陸海升溫不同造成空氣對流</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>傳導(熱由手傳向冰)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>對流</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>太空中無介質太陽熱如何傳到地球？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>傳導</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>良導體</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>輻射</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>輻射</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上5-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>固體為主</t>
+          <t>固體為主：傳導是熱能靠鄰近粒子一個接一個碰撞把振動能量傳遞出去的方式，主要發生在固體中</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>液氣</t>
+          <t>液氣：對流是液體或氣體受熱後整體流動，把熱能帶到別處的傳播方式，主要發生在液態和氣態</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>不需介質</t>
+          <t>不需介質：輻射是以電磁波的形式傳遞熱能，不需要靠介質分子傳遞，即使在真空中也能傳播</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>傳導快</t>
+          <t>傳導快：金屬內部有許多可自由移動的電子，能快速把熱能傳遞出去，所以金屬是熱的良導體</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>真空可</t>
+          <t>真空可：輻射是以電磁波形式傳遞能量，不需要靠介質分子傳遞，所以在真空中也能傳播熱能</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>冷下降</t>
+          <t>冷下降：流體受熱後體積膨脹、密度變小，會往上升，密度較大的冷流體則往下沉補充，形成對流循環</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>真空傳播</t>
+          <t>真空傳播：太陽和地球之間是接近真空的太空，沒有介質可以傳導或對流，太陽的熱能是以輻射的方式跨越太空傳到地球</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>保溫</t>
+          <t>保溫：空氣分子間距離大，傳導熱能的效率很差，是熱的不良導體，這也是許多保暖材料利用空氣層隔熱的原因</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>三種</t>
+          <t>三種：熱能傳播的三種基本方式是傳導、對流、輻射</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>絕熱</t>
+          <t>絕熱：木頭是熱的不良導體，傳導熱量的速度很慢，用木頭做鍋子把手可以避免燙手</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>沿金屬</t>
+          <t>沿金屬：熱湯的熱能透過金屬湯匙中緊密排列的粒子，一路碰撞傳導到手握的匙柄部位，這是傳導的現象</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>水循環</t>
+          <t>水循環：底部的水受熱後密度變小往上升，上方較冷的水往下補充再受熱上升，形成循環流動，把整鍋水加熱，這是對流</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>循環佳</t>
+          <t>循環佳：冷氣機吹出的冷空氣密度較大會往下沉，裝在高處可以讓冷空氣自然下降、與室內空氣形成良好的對流循環，均勻降溫</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>對流</t>
+          <t>對流：暖氣機加熱的空氣密度變小會往上升，裝在低處可以讓熱空氣由下往上自然對流，均勻加溫整個房間</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：保溫瓶內層鍍銀使表面光亮，能把輻射熱反射回去，減少熱能以輻射方式散失或進入</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>粒子不流動</t>
+          <t>粒子不流動：對流需要流體整體流動來帶動熱能傳遞，固體的粒子被固定在原位無法自由流動，所以固體不能對流</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>輻射吸收</t>
+          <t>輻射吸收：深色物體吸收輻射熱的能力較強，較容易吸收陽光等輻射熱能，所以深色衣物在陽光下通常感覺比較熱</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>阻傳導</t>
+          <t>阻傳導：羽絨衣蓬鬆的羽絨中包覆了大量靜止空氣，空氣是熱的不良導體，能有效阻隔身體熱量透過傳導散失，達到保暖效果</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>輻射</t>
+          <t>輻射：火源不需要接觸也不需要介質，就能以輻射的方式把熱能直接傳給附近的手，讓人感覺溫暖</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>對流</t>
+          <t>對流：液體和氣體受熱後密度變小、往上流動，冷的部分再往下補充，形成循環流動，這種傳熱方式稱為對流</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>綜合設計</t>
+          <t>綜合設計：保溫瓶夾層抽成真空，沒有介質可以傳導或對流；內壁鍍銀能把輻射熱反射回去，這樣的設計同時阻隔了傳導、對流、輻射三種傳熱方式，達到良好的保溫效果</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：陸地和海洋升溫降溫速率不同，造成兩地上方空氣溫度、密度不同，熱空氣上升、冷空氣補充流入，形成大規模的空氣對流循環，就是海陸風</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>對流</t>
+          <t>對流：燃燒產生的熱氣密度小往上升通過煙囪排出，下方新鮮空氣(含氧氣)因對流被抽入補充，源源不絕供應氧氣，有助於燃燒持續進行</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>面積</t>
+          <t>面積：把散熱片做成多片鰭狀，可以大幅增加與空氣接觸的表面積，讓熱能能更快速地透過傳導和對流散失出去</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>輻射</t>
+          <t>輻射：沙漠空氣乾燥、缺乏水氣和雲層阻隔，夜間地表的熱能容易快速以輻射方式散失到太空中，使氣溫快速下降，造成日夜溫差很大</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>無介質</t>
+          <t>無介質：真空中沒有介質分子可以傳導或對流，兩物體之間只能靠不需要介質的輻射方式傳遞熱能</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>方向</t>
+          <t>方向：手和冰塊直接接觸，手的熱能透過粒子碰撞(傳導)流向溫度較低的冰塊，手因為失去熱量而感覺冷</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：淺色表面能反射較多的太陽輻射熱，吸收的熱能較少，所以淺色屋頂下方溫度通常比深色屋頂涼爽</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>對流</t>
+          <t>對流：空氣受熱後體積膨脹、密度變小，比周圍冷空氣輕，因此會往上升，冷空氣則往下補充，形成對流循環</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>輻射</t>
+          <t>輻射：太陽和地球之間是接近真空的太空，沒有介質可以傳導或對流，太陽的熱能是以輻射(電磁波)的方式跨越太空傳到地球</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上5-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-3_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>傳導對流輻射</t>
+          <t>輻射</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>輻射</t>
+          <t>良導體</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>良導體</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>熱空氣上升</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>吸熱</t>
+          <t>空氣不良導體</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>只能靠輻射</t>
+          <t>輻射</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>對流</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>空氣不良導體</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>上升</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>只能靠輻射</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>傳導</t>
+          <t>傳導對流輻射</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>傳導對流輻射</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>吸熱</t>
+          <t>上升</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -723,17 +723,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>傳導對流輻射</t>
+          <t>空氣不良導體</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>不良導體</t>
+          <t>良導體</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>良導體</t>
+          <t>傳導</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>傳導</t>
+          <t>良導體</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>良導體</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>對流</t>
+          <t>空氣不良導體</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>熱空氣上升</t>
+          <t>不良導體</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>對流</t>
+          <t>上升</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>不良導體</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
           <t>傳導</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>不良導體</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>吸熱</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>輻射</t>
+          <t>熱空氣上升</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>傳導</t>
+          <t>上升</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>對流</t>
+          <t>不良導體</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>傳導對流輻射</t>
+          <t>吸熱</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>熱空氣上升</t>
+          <t>上升</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>良導體</t>
+          <t>熱空氣上升</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>對流</t>
+          <t>只能靠輻射</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>吸熱</t>
+          <t>上升</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>傳導</t>
+          <t>熱空氣上升</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>良導體</t>
+          <t>只能靠輻射</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>輻射</t>
+          <t>上升</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1159,17 +1159,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>輻射</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>傳導對流輻射</t>
+          <t>只能靠輻射</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>上升</t>
+          <t>吸熱</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>吸熱</t>
+          <t>熱空氣上升</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>上升</t>
+          <t>對流</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>只能靠輻射</t>
+          <t>傳導</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>吸熱</t>
+          <t>傳導對流輻射</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>傳導</t>
+          <t>熱空氣上升</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>只能靠輻射</t>
+          <t>對流</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>傳導</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>上升</t>
+          <t>熱空氣上升</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1720,17 +1720,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>對流</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>不良導體</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>空氣不良導體</t>
-        </is>
-      </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>傳導對流輻射</t>
+          <t>良導體</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>傳導</t>
+          <t>不良導體</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>上升</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>良導體</t>
+          <t>對流</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
